--- a/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:52</t>
+          <t>2026-09-02 01:22:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:52</t>
+          <t>2026-09-02 01:22:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:52</t>
+          <t>2026-09-02 01:22:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:52</t>
+          <t>2026-09-02 01:22:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:53</t>
+          <t>2026-09-02 01:22:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:53</t>
+          <t>2026-09-02 01:22:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:53</t>
+          <t>2026-09-02 01:22:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:53</t>
+          <t>2026-09-02 01:22:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:54</t>
+          <t>2026-09-02 01:22:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:54</t>
+          <t>2026-09-02 01:22:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:54</t>
+          <t>2026-09-02 01:22:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:54</t>
+          <t>2026-09-02 01:22:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:54</t>
+          <t>2026-09-02 01:22:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:54</t>
+          <t>2026-09-02 01:22:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:56</t>
+          <t>2026-09-02 01:22:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:07</t>
+          <t>2026-09-02 16:26:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>-3.46%5445</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:07</t>
+          <t>2026-09-02 16:26:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+0.21%973</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>973</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:07</t>
+          <t>2026-09-02 16:26:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>-2.25%2385</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:07</t>
+          <t>2026-09-02 16:26:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:08</t>
+          <t>2026-09-02 16:26:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:08</t>
+          <t>2026-09-02 16:26:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:08</t>
+          <t>2026-09-02 16:26:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:08</t>
+          <t>2026-09-02 16:26:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>-0.93%4275</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:10</t>
+          <t>2026-09-02 16:26:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:10</t>
+          <t>2026-09-02 16:26:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-2.22%5290</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:10</t>
+          <t>2026-09-02 16:26:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>589</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:10</t>
+          <t>2026-09-02 16:26:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>-2.04%1200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:10</t>
+          <t>2026-09-02 16:26:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:10</t>
+          <t>2026-09-02 16:26:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:11</t>
+          <t>2026-09-02 16:26:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+8.56%279</t>
+          <t>-3.05%270.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+8.56%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>270.5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">

--- a/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:06</t>
+          <t>2026-09-02 19:49:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:06</t>
+          <t>2026-09-02 19:49:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:06</t>
+          <t>2026-09-02 19:49:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:06</t>
+          <t>2026-09-02 19:49:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:07</t>
+          <t>2026-09-02 19:49:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:07</t>
+          <t>2026-09-02 19:49:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:07</t>
+          <t>2026-09-02 19:49:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:07</t>
+          <t>2026-09-02 19:49:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:08</t>
+          <t>2026-09-02 19:49:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:08</t>
+          <t>2026-09-02 19:49:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:08</t>
+          <t>2026-09-02 19:49:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:08</t>
+          <t>2026-09-02 19:49:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:08</t>
+          <t>2026-09-02 19:49:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:08</t>
+          <t>2026-09-02 19:49:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:10</t>
+          <t>2026-09-02 19:49:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:23</t>
+          <t>2026-09-02 22:21:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:23</t>
+          <t>2026-09-02 22:21:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:23</t>
+          <t>2026-09-02 22:21:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:23</t>
+          <t>2026-09-02 22:21:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:25</t>
+          <t>2026-09-02 22:21:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:25</t>
+          <t>2026-09-02 22:21:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:25</t>
+          <t>2026-09-02 22:21:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:25</t>
+          <t>2026-09-02 22:21:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:26</t>
+          <t>2026-09-02 22:21:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:26</t>
+          <t>2026-09-02 22:21:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:26</t>
+          <t>2026-09-02 22:21:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:26</t>
+          <t>2026-09-02 22:21:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:26</t>
+          <t>2026-09-02 22:21:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:26</t>
+          <t>2026-09-02 22:21:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:27</t>
+          <t>2026-09-02 22:21:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:23</t>
+          <t>2026-09-02 23:18:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:23</t>
+          <t>2026-09-02 23:18:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:23</t>
+          <t>2026-09-02 23:18:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:23</t>
+          <t>2026-09-02 23:18:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:25</t>
+          <t>2026-09-02 23:18:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:25</t>
+          <t>2026-09-02 23:18:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:25</t>
+          <t>2026-09-02 23:18:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:25</t>
+          <t>2026-09-02 23:18:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:26</t>
+          <t>2026-09-02 23:18:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:26</t>
+          <t>2026-09-02 23:18:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:26</t>
+          <t>2026-09-02 23:18:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:26</t>
+          <t>2026-09-02 23:18:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:26</t>
+          <t>2026-09-02 23:18:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:26</t>
+          <t>2026-09-02 23:18:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 22:21:27</t>
+          <t>2026-09-02 23:18:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
